--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R244-CategorieOrganisation.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R244-CategorieOrganisation.xlsx
@@ -2206,7 +2206,7 @@
     <t>Centre du sommeil</t>
   </si>
   <si>
-    <t>Structure de relayage au domicile</t>
+    <t>Offre de relayage au domicile</t>
   </si>
 </sst>
 </file>
